--- a/public/files/uhc_medical_equipment.xlsx
+++ b/public/files/uhc_medical_equipment.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\UHC Project Proposal\Equipments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Laragon-root\www\pwd_asset\public\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB85B28-18F4-4C8B-B3B7-E5E7233914B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D3A22B-A37A-41CE-83B5-090187DD3941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Medical Equipment" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Medical Equipment'!$A$12:$E$141</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Medical Equipment'!$A$1:$E$275</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Medical Equipment'!$A$1:$E$179</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Medical Equipment'!$12:$12</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="162">
   <si>
     <t>SL</t>
   </si>
@@ -413,201 +413,24 @@
     <t>Furniture</t>
   </si>
   <si>
-    <t>Patient Examination Table</t>
-  </si>
-  <si>
-    <t>Patient Beds (fowler bed) with Bedside Lockers</t>
-  </si>
-  <si>
-    <t>Tables</t>
-  </si>
-  <si>
-    <t>Dispensing tables</t>
-  </si>
-  <si>
-    <t>Chairs</t>
-  </si>
-  <si>
-    <t>Wheelchair</t>
-  </si>
-  <si>
-    <t>Stool</t>
-  </si>
-  <si>
-    <t>Benches with Back Rest</t>
-  </si>
-  <si>
-    <t>Electric Fans</t>
-  </si>
-  <si>
-    <t>Air-Conditioners</t>
-  </si>
-  <si>
-    <t>Racks</t>
-  </si>
-  <si>
-    <t>Almirah</t>
-  </si>
-  <si>
-    <t>Stretchers</t>
-  </si>
-  <si>
-    <t>Drip stand</t>
-  </si>
-  <si>
-    <t>Patient Trolley</t>
-  </si>
-  <si>
-    <t>Food trolley</t>
-  </si>
-  <si>
-    <t>Medicine trolley</t>
-  </si>
-  <si>
-    <t>Trolley for instruments</t>
-  </si>
-  <si>
-    <t>Multiple registers</t>
-  </si>
-  <si>
     <t>Facility infrastructure</t>
   </si>
   <si>
-    <t>Deep tube well with electric motor</t>
-  </si>
-  <si>
-    <t>Sanitation sewage system</t>
-  </si>
-  <si>
-    <t>Central oxygen system</t>
-  </si>
-  <si>
-    <t>Air conditioners</t>
-  </si>
-  <si>
-    <t>Electric fans and lights</t>
-  </si>
-  <si>
     <t>Medical Waste Management</t>
   </si>
   <si>
-    <t>Black Bin</t>
-  </si>
-  <si>
-    <t>Yellow Bin</t>
-  </si>
-  <si>
-    <t>Red Bin</t>
-  </si>
-  <si>
-    <t>Green Bin</t>
-  </si>
-  <si>
-    <t>Blue bin</t>
-  </si>
-  <si>
-    <t>Bowl (Blue)</t>
-  </si>
-  <si>
-    <t>Biohazard bags</t>
-  </si>
-  <si>
-    <t>Waste bags</t>
-  </si>
-  <si>
     <t>Waste Carrying Trolly</t>
   </si>
   <si>
-    <t>Heavy duty gloves</t>
-  </si>
-  <si>
-    <t>PPE Equipment</t>
-  </si>
-  <si>
     <t>Infection Prevention</t>
   </si>
   <si>
-    <t>Soap</t>
-  </si>
-  <si>
-    <t>Sanitizer</t>
-  </si>
-  <si>
-    <t>Running water</t>
-  </si>
-  <si>
-    <t>Disinfectant</t>
-  </si>
-  <si>
-    <t>Detergent</t>
-  </si>
-  <si>
-    <t>Hand gloves</t>
-  </si>
-  <si>
-    <t>Buckets, bowls, mugs, brushes, brooms, dusters &amp; others</t>
-  </si>
-  <si>
-    <t>Toilet cleaner</t>
-  </si>
-  <si>
-    <t>Phenyl</t>
-  </si>
-  <si>
     <t>Sterilizer</t>
   </si>
   <si>
     <t>Needle crusher</t>
   </si>
   <si>
-    <t>Surgical masks and caps</t>
-  </si>
-  <si>
-    <t>Eye protector</t>
-  </si>
-  <si>
-    <t>Apron</t>
-  </si>
-  <si>
-    <t>Consumables</t>
-  </si>
-  <si>
-    <t>Syringes and needles</t>
-  </si>
-  <si>
-    <t>Gauze</t>
-  </si>
-  <si>
-    <t>Bandage</t>
-  </si>
-  <si>
-    <t>Latex gloves or Hand gloves</t>
-  </si>
-  <si>
-    <t>Strips for RDT</t>
-  </si>
-  <si>
-    <t>Cotton Wool</t>
-  </si>
-  <si>
-    <t>Laboratory reagents</t>
-  </si>
-  <si>
-    <t>X-ray films</t>
-  </si>
-  <si>
-    <t>Blood Bags</t>
-  </si>
-  <si>
-    <t>Safety</t>
-  </si>
-  <si>
-    <t>Firefighting equipment (extinguisher, blanket etc.)</t>
-  </si>
-  <si>
-    <t>CCTV cameras</t>
-  </si>
-  <si>
     <t>Vehicles</t>
   </si>
   <si>
@@ -617,9 +440,6 @@
     <t>Vehicle for UH&amp;FPO</t>
   </si>
   <si>
-    <t>Others</t>
-  </si>
-  <si>
     <t>Biometric machine for attendance</t>
   </si>
   <si>
@@ -644,12 +464,6 @@
     <t>* A signed copy of this document need to upload too.</t>
   </si>
   <si>
-    <t>Section B: Logistic Equipment</t>
-  </si>
-  <si>
-    <t>Section A: Medical Service Equipment</t>
-  </si>
-  <si>
     <t>Blood transfusion bed (Unit also includes chair, refrigerator, blood tube sealer, blood transfusion set (source footnote 82))</t>
   </si>
   <si>
@@ -665,24 +479,12 @@
     <t>Digital Display Unit (nos)</t>
   </si>
   <si>
-    <t>Scanner</t>
-  </si>
-  <si>
-    <t>Printer</t>
-  </si>
-  <si>
-    <t>Photocopyer</t>
-  </si>
-  <si>
     <t>Qty</t>
   </si>
   <si>
     <t>Remarks/Condition</t>
   </si>
   <si>
-    <t>Section C: Others (provide if anything is not mentioned above but worth mentioning)</t>
-  </si>
-  <si>
     <t>Information Provider</t>
   </si>
   <si>
@@ -701,10 +503,19 @@
     <t>Information Provider:</t>
   </si>
   <si>
-    <t>Spade and other digging tools (For waste pit)</t>
-  </si>
-  <si>
-    <t>Solar panel</t>
+    <t>Other Logistic</t>
+  </si>
+  <si>
+    <t>Central oxygen system (VIE Tank)</t>
+  </si>
+  <si>
+    <t>Trolley for instrument</t>
+  </si>
+  <si>
+    <t>Section A: Medical Service Equipment (only col D and E are editable, Qty is in nos)</t>
+  </si>
+  <si>
+    <t>Section B: Others (provide if anything is not mentioned above but worth mentioning)  (Qty is is nos, only col D and E are editable)</t>
   </si>
 </sst>
 </file>
@@ -863,7 +674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -908,9 +719,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -946,10 +754,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1237,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E273"/>
+  <dimension ref="A1:E179"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" style="11" customWidth="1"/>
@@ -1249,101 +1053,101 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
-      <c r="E1" s="32"/>
+      <c r="E1" s="30"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
-      <c r="E2" s="33"/>
+      <c r="E2" s="31"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
-      <c r="E3" s="33"/>
+      <c r="E3" s="31"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="24">
+      <c r="A4" s="23">
         <v>1</v>
       </c>
-      <c r="B4" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="C4" s="26"/>
+      <c r="B4" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="25"/>
       <c r="D4" s="12"/>
-      <c r="E4" s="33"/>
+      <c r="E4" s="31"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="24">
+      <c r="A5" s="23">
         <v>2</v>
       </c>
-      <c r="B5" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" s="26"/>
+      <c r="B5" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="25"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="33"/>
+      <c r="E5" s="31"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="24">
+      <c r="A6" s="23">
         <v>3</v>
       </c>
-      <c r="B6" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" s="26"/>
+      <c r="B6" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="25"/>
       <c r="D6" s="12"/>
-      <c r="E6" s="33"/>
+      <c r="E6" s="31"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="24">
+      <c r="A7" s="23">
         <v>4</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="C7" s="26"/>
+      <c r="B7" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="25"/>
       <c r="D7" s="12"/>
-      <c r="E7" s="33"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="24">
+      <c r="A8" s="23">
         <v>5</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="C8" s="26"/>
+      <c r="B8" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="25"/>
       <c r="D8" s="12"/>
-      <c r="E8" s="33"/>
+      <c r="E8" s="31"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="33"/>
+      <c r="E9" s="31"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="35"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>205</v>
+      <c r="A11" s="19" t="s">
+        <v>160</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1354,17 +1158,17 @@
       <c r="A12" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>219</v>
+      <c r="B12" s="22" t="s">
+        <v>153</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>215</v>
+      <c r="D12" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="27" x14ac:dyDescent="0.25">
@@ -1386,125 +1190,125 @@
       <c r="C14" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="31"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="29"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>2</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="28"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="27"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>3</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="27"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>4</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="31"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>5</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="27"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>6</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="27"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>7</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="27"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>8</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="27"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>9</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="27"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>10</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="27"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
@@ -1525,21 +1329,21 @@
       <c r="C25" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="27"/>
-      <c r="E25" s="28"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="27"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>12</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="28"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="27"/>
     </row>
     <row r="27" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
@@ -1560,593 +1364,593 @@
       <c r="C28" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="28"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="27"/>
     </row>
     <row r="29" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>14</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="27"/>
-      <c r="E29" s="28"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="27"/>
     </row>
     <row r="30" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>15</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="28"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="27"/>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>16</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="27"/>
-      <c r="E31" s="28"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="27"/>
     </row>
     <row r="32" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>17</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="28"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="27"/>
     </row>
     <row r="33" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>18</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="27"/>
-      <c r="E33" s="28"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="27"/>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>19</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="28"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="27"/>
     </row>
     <row r="35" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>20</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="28"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="27"/>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>21</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="27"/>
-      <c r="E36" s="28"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="27"/>
     </row>
     <row r="37" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>22</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="27"/>
-      <c r="E37" s="28"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="27"/>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>23</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D38" s="27"/>
-      <c r="E38" s="28"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="27"/>
     </row>
     <row r="39" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>24</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="27"/>
-      <c r="E39" s="28"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="27"/>
     </row>
     <row r="40" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>25</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D40" s="27"/>
-      <c r="E40" s="28"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="27"/>
     </row>
     <row r="41" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>26</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="28"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="27"/>
     </row>
     <row r="42" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>27</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D42" s="27"/>
-      <c r="E42" s="28"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="27"/>
     </row>
     <row r="43" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>28</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="27"/>
-      <c r="E43" s="28"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="27"/>
     </row>
     <row r="44" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>29</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D44" s="27"/>
-      <c r="E44" s="28"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="27"/>
     </row>
     <row r="45" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>30</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D45" s="27"/>
-      <c r="E45" s="28"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="27"/>
     </row>
     <row r="46" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <v>31</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D46" s="27"/>
-      <c r="E46" s="28"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="27"/>
     </row>
     <row r="47" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <v>32</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D47" s="27"/>
-      <c r="E47" s="28"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="27"/>
     </row>
     <row r="48" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
         <v>33</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D48" s="27"/>
-      <c r="E48" s="28"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="27"/>
     </row>
     <row r="49" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A49" s="10">
         <v>34</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D49" s="27"/>
-      <c r="E49" s="28"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="27"/>
     </row>
     <row r="50" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <v>35</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D50" s="27"/>
-      <c r="E50" s="28"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="27"/>
     </row>
     <row r="51" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>36</v>
       </c>
-      <c r="B51" s="17" t="s">
+      <c r="B51" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D51" s="27"/>
-      <c r="E51" s="28"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="27"/>
     </row>
     <row r="52" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>37</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D52" s="27"/>
-      <c r="E52" s="28"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="27"/>
     </row>
     <row r="53" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>38</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D53" s="27"/>
-      <c r="E53" s="28"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="27"/>
     </row>
     <row r="54" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>39</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B54" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D54" s="27"/>
-      <c r="E54" s="28"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="27"/>
     </row>
     <row r="55" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>40</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="B55" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="27"/>
-      <c r="E55" s="28"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="27"/>
     </row>
     <row r="56" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>41</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D56" s="27"/>
-      <c r="E56" s="28"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="27"/>
     </row>
     <row r="57" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>42</v>
       </c>
-      <c r="B57" s="17" t="s">
+      <c r="B57" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D57" s="27"/>
-      <c r="E57" s="28"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="27"/>
     </row>
     <row r="58" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>43</v>
       </c>
-      <c r="B58" s="17" t="s">
+      <c r="B58" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D58" s="27"/>
-      <c r="E58" s="28"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="27"/>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>44</v>
       </c>
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D59" s="27"/>
-      <c r="E59" s="28"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="27"/>
     </row>
     <row r="60" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A60" s="10">
         <v>45</v>
       </c>
-      <c r="B60" s="17" t="s">
+      <c r="B60" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="27"/>
-      <c r="E60" s="28"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="27"/>
     </row>
     <row r="61" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>46</v>
       </c>
-      <c r="B61" s="17" t="s">
+      <c r="B61" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D61" s="27"/>
-      <c r="E61" s="28"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="27"/>
     </row>
     <row r="62" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>47</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D62" s="27"/>
-      <c r="E62" s="28"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="27"/>
     </row>
     <row r="63" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>48</v>
       </c>
-      <c r="B63" s="17" t="s">
+      <c r="B63" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D63" s="27"/>
-      <c r="E63" s="28"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="27"/>
     </row>
     <row r="64" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>49</v>
       </c>
-      <c r="B64" s="17" t="s">
+      <c r="B64" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D64" s="27"/>
-      <c r="E64" s="28"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="27"/>
     </row>
     <row r="65" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>50</v>
       </c>
-      <c r="B65" s="17" t="s">
+      <c r="B65" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D65" s="27"/>
-      <c r="E65" s="28"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="27"/>
     </row>
     <row r="66" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>51</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D66" s="27"/>
-      <c r="E66" s="28"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="27"/>
     </row>
     <row r="67" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>52</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B67" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D67" s="27"/>
-      <c r="E67" s="28"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="27"/>
     </row>
     <row r="68" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>53</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B68" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C68" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D68" s="27"/>
-      <c r="E68" s="28"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="27"/>
     </row>
     <row r="69" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>54</v>
       </c>
-      <c r="B69" s="17" t="s">
+      <c r="B69" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D69" s="27"/>
-      <c r="E69" s="28"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="27"/>
     </row>
     <row r="70" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>55</v>
       </c>
-      <c r="B70" s="17" t="s">
+      <c r="B70" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D70" s="27"/>
-      <c r="E70" s="28"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="27"/>
     </row>
     <row r="71" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>56</v>
       </c>
-      <c r="B71" s="17" t="s">
+      <c r="B71" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D71" s="27"/>
-      <c r="E71" s="28"/>
+      <c r="D71" s="26"/>
+      <c r="E71" s="27"/>
     </row>
     <row r="72" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>57</v>
       </c>
-      <c r="B72" s="18" t="s">
+      <c r="B72" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C72" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D72" s="27"/>
-      <c r="E72" s="28"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="27"/>
     </row>
     <row r="73" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>58</v>
       </c>
-      <c r="B73" s="17" t="s">
+      <c r="B73" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D73" s="27"/>
-      <c r="E73" s="28"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="27"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="9"/>
@@ -2167,47 +1971,47 @@
       <c r="C75" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D75" s="27"/>
-      <c r="E75" s="28"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="27"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>60</v>
       </c>
-      <c r="B76" s="17" t="s">
+      <c r="B76" s="16" t="s">
         <v>63</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D76" s="27"/>
-      <c r="E76" s="28"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="27"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>61</v>
       </c>
-      <c r="B77" s="17" t="s">
+      <c r="B77" s="16" t="s">
         <v>63</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D77" s="27"/>
-      <c r="E77" s="28"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="27"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>62</v>
       </c>
-      <c r="B78" s="17" t="s">
+      <c r="B78" s="16" t="s">
         <v>63</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D78" s="27"/>
-      <c r="E78" s="28"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="27"/>
     </row>
     <row r="79" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A79" s="9"/>
@@ -2228,190 +2032,190 @@
       <c r="C80" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D80" s="27"/>
-      <c r="E80" s="28"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="27"/>
     </row>
     <row r="81" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>64</v>
       </c>
-      <c r="B81" s="17" t="s">
+      <c r="B81" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D81" s="27"/>
-      <c r="E81" s="28"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="27"/>
     </row>
     <row r="82" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>65</v>
       </c>
-      <c r="B82" s="17" t="s">
+      <c r="B82" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C82" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D82" s="27"/>
-      <c r="E82" s="28"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="27"/>
     </row>
     <row r="83" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>66</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B83" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="27"/>
-      <c r="E83" s="28"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="27"/>
     </row>
     <row r="84" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>67</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B84" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C84" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="D84" s="27"/>
-      <c r="E84" s="28"/>
+      <c r="C84" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="D84" s="26"/>
+      <c r="E84" s="27"/>
     </row>
     <row r="85" spans="1:5" ht="54" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>68</v>
       </c>
-      <c r="B85" s="17" t="s">
+      <c r="B85" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C85" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="D85" s="27"/>
-      <c r="E85" s="28"/>
+      <c r="C85" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="D85" s="26"/>
+      <c r="E85" s="27"/>
     </row>
     <row r="86" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>69</v>
       </c>
-      <c r="B86" s="17" t="s">
+      <c r="B86" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C86" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D86" s="27"/>
-      <c r="E86" s="28"/>
+      <c r="D86" s="26"/>
+      <c r="E86" s="27"/>
     </row>
     <row r="87" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>70</v>
       </c>
-      <c r="B87" s="17" t="s">
+      <c r="B87" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D87" s="27"/>
-      <c r="E87" s="28"/>
+      <c r="D87" s="26"/>
+      <c r="E87" s="27"/>
     </row>
     <row r="88" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>71</v>
       </c>
-      <c r="B88" s="17" t="s">
+      <c r="B88" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D88" s="27"/>
-      <c r="E88" s="28"/>
+      <c r="D88" s="26"/>
+      <c r="E88" s="27"/>
     </row>
     <row r="89" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>72</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D89" s="27"/>
-      <c r="E89" s="28"/>
+      <c r="D89" s="26"/>
+      <c r="E89" s="27"/>
     </row>
     <row r="90" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>73</v>
       </c>
-      <c r="B90" s="17" t="s">
+      <c r="B90" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C90" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D90" s="27"/>
-      <c r="E90" s="28"/>
+      <c r="D90" s="26"/>
+      <c r="E90" s="27"/>
     </row>
     <row r="91" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>74</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B91" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D91" s="27"/>
-      <c r="E91" s="28"/>
+      <c r="D91" s="26"/>
+      <c r="E91" s="27"/>
     </row>
     <row r="92" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>75</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B92" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D92" s="27"/>
-      <c r="E92" s="28"/>
+      <c r="D92" s="26"/>
+      <c r="E92" s="27"/>
     </row>
     <row r="93" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>76</v>
       </c>
-      <c r="B93" s="17" t="s">
+      <c r="B93" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C93" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D93" s="27"/>
-      <c r="E93" s="28"/>
+      <c r="D93" s="26"/>
+      <c r="E93" s="27"/>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>77</v>
       </c>
-      <c r="B94" s="17" t="s">
+      <c r="B94" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D94" s="27"/>
-      <c r="E94" s="28"/>
+      <c r="D94" s="26"/>
+      <c r="E94" s="27"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="9"/>
@@ -2432,47 +2236,47 @@
       <c r="C96" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D96" s="27"/>
-      <c r="E96" s="28"/>
+      <c r="D96" s="26"/>
+      <c r="E96" s="27"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>79</v>
       </c>
-      <c r="B97" s="17" t="s">
+      <c r="B97" s="16" t="s">
         <v>82</v>
       </c>
       <c r="C97" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D97" s="27"/>
-      <c r="E97" s="28"/>
+      <c r="D97" s="26"/>
+      <c r="E97" s="27"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>80</v>
       </c>
-      <c r="B98" s="18" t="s">
+      <c r="B98" s="17" t="s">
         <v>82</v>
       </c>
       <c r="C98" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D98" s="27"/>
-      <c r="E98" s="28"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="27"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>81</v>
       </c>
-      <c r="B99" s="17" t="s">
+      <c r="B99" s="16" t="s">
         <v>82</v>
       </c>
       <c r="C99" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D99" s="27"/>
-      <c r="E99" s="28"/>
+      <c r="D99" s="26"/>
+      <c r="E99" s="27"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="9"/>
@@ -2493,47 +2297,47 @@
       <c r="C101" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D101" s="27"/>
-      <c r="E101" s="28"/>
+      <c r="D101" s="26"/>
+      <c r="E101" s="27"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="10">
         <v>83</v>
       </c>
-      <c r="B102" s="17" t="s">
+      <c r="B102" s="16" t="s">
         <v>87</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D102" s="27"/>
-      <c r="E102" s="28"/>
+      <c r="D102" s="26"/>
+      <c r="E102" s="27"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>84</v>
       </c>
-      <c r="B103" s="17" t="s">
+      <c r="B103" s="16" t="s">
         <v>87</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D103" s="27"/>
-      <c r="E103" s="28"/>
+      <c r="D103" s="26"/>
+      <c r="E103" s="27"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>85</v>
       </c>
-      <c r="B104" s="17" t="s">
+      <c r="B104" s="16" t="s">
         <v>87</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D104" s="27"/>
-      <c r="E104" s="28"/>
+      <c r="D104" s="26"/>
+      <c r="E104" s="27"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="9"/>
@@ -2554,47 +2358,47 @@
       <c r="C106" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D106" s="27"/>
-      <c r="E106" s="28"/>
+      <c r="D106" s="26"/>
+      <c r="E106" s="27"/>
     </row>
     <row r="107" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>87</v>
       </c>
-      <c r="B107" s="18" t="s">
+      <c r="B107" s="17" t="s">
         <v>92</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D107" s="27"/>
-      <c r="E107" s="28"/>
+      <c r="D107" s="26"/>
+      <c r="E107" s="27"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>88</v>
       </c>
-      <c r="B108" s="17" t="s">
+      <c r="B108" s="16" t="s">
         <v>92</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D108" s="27"/>
-      <c r="E108" s="28"/>
+      <c r="D108" s="26"/>
+      <c r="E108" s="27"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="10">
         <v>89</v>
       </c>
-      <c r="B109" s="17" t="s">
+      <c r="B109" s="16" t="s">
         <v>92</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D109" s="27"/>
-      <c r="E109" s="28"/>
+      <c r="D109" s="26"/>
+      <c r="E109" s="27"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="9"/>
@@ -2615,47 +2419,47 @@
       <c r="C111" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D111" s="27"/>
-      <c r="E111" s="28"/>
+      <c r="D111" s="26"/>
+      <c r="E111" s="27"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="10">
         <v>91</v>
       </c>
-      <c r="B112" s="17" t="s">
+      <c r="B112" s="16" t="s">
         <v>96</v>
       </c>
       <c r="C112" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D112" s="27"/>
-      <c r="E112" s="28"/>
+      <c r="D112" s="26"/>
+      <c r="E112" s="27"/>
     </row>
     <row r="113" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>92</v>
       </c>
-      <c r="B113" s="17" t="s">
+      <c r="B113" s="16" t="s">
         <v>96</v>
       </c>
       <c r="C113" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D113" s="27"/>
-      <c r="E113" s="28"/>
+      <c r="D113" s="26"/>
+      <c r="E113" s="27"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="10">
         <v>93</v>
       </c>
-      <c r="B114" s="17" t="s">
+      <c r="B114" s="16" t="s">
         <v>96</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D114" s="27"/>
-      <c r="E114" s="28"/>
+      <c r="D114" s="26"/>
+      <c r="E114" s="27"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="9"/>
@@ -2673,37 +2477,37 @@
       <c r="B116" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C116" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="D116" s="27"/>
-      <c r="E116" s="28"/>
+      <c r="C116" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="D116" s="26"/>
+      <c r="E116" s="27"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="10">
         <v>95</v>
       </c>
-      <c r="B117" s="17" t="s">
+      <c r="B117" s="16" t="s">
         <v>101</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D117" s="27"/>
-      <c r="E117" s="28"/>
+      <c r="D117" s="26"/>
+      <c r="E117" s="27"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="10">
         <v>96</v>
       </c>
-      <c r="B118" s="17" t="s">
+      <c r="B118" s="16" t="s">
         <v>101</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D118" s="27"/>
-      <c r="E118" s="28"/>
+      <c r="D118" s="26"/>
+      <c r="E118" s="27"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="9"/>
@@ -2724,47 +2528,47 @@
       <c r="C120" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D120" s="27"/>
-      <c r="E120" s="28"/>
+      <c r="D120" s="26"/>
+      <c r="E120" s="27"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="10">
         <v>98</v>
       </c>
-      <c r="B121" s="17" t="s">
+      <c r="B121" s="16" t="s">
         <v>104</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D121" s="27"/>
-      <c r="E121" s="28"/>
+      <c r="D121" s="26"/>
+      <c r="E121" s="27"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="10">
         <v>99</v>
       </c>
-      <c r="B122" s="17" t="s">
+      <c r="B122" s="16" t="s">
         <v>104</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D122" s="27"/>
-      <c r="E122" s="28"/>
+      <c r="D122" s="26"/>
+      <c r="E122" s="27"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="10">
         <v>100</v>
       </c>
-      <c r="B123" s="17" t="s">
+      <c r="B123" s="16" t="s">
         <v>104</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="D123" s="27"/>
-      <c r="E123" s="28"/>
+      <c r="D123" s="26"/>
+      <c r="E123" s="27"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="9"/>
@@ -2785,243 +2589,269 @@
       <c r="C125" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D125" s="27"/>
-      <c r="E125" s="28"/>
+      <c r="D125" s="26"/>
+      <c r="E125" s="27"/>
     </row>
     <row r="126" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A126" s="10">
         <v>102</v>
       </c>
-      <c r="B126" s="17" t="s">
+      <c r="B126" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D126" s="27"/>
-      <c r="E126" s="28"/>
+      <c r="D126" s="26"/>
+      <c r="E126" s="27"/>
     </row>
     <row r="127" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A127" s="10">
         <v>103</v>
       </c>
-      <c r="B127" s="17" t="s">
+      <c r="B127" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D127" s="27"/>
-      <c r="E127" s="28"/>
+      <c r="D127" s="26"/>
+      <c r="E127" s="27"/>
     </row>
     <row r="128" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A128" s="10">
         <v>104</v>
       </c>
-      <c r="B128" s="17" t="s">
+      <c r="B128" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D128" s="27"/>
-      <c r="E128" s="28"/>
+      <c r="D128" s="26"/>
+      <c r="E128" s="27"/>
     </row>
     <row r="129" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A129" s="10">
         <v>105</v>
       </c>
-      <c r="B129" s="17" t="s">
+      <c r="B129" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D129" s="27"/>
-      <c r="E129" s="28"/>
+      <c r="D129" s="26"/>
+      <c r="E129" s="27"/>
     </row>
     <row r="130" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A130" s="10">
         <v>106</v>
       </c>
-      <c r="B130" s="17" t="s">
+      <c r="B130" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D130" s="27"/>
-      <c r="E130" s="28"/>
+      <c r="D130" s="26"/>
+      <c r="E130" s="27"/>
     </row>
     <row r="131" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A131" s="10">
         <v>107</v>
       </c>
-      <c r="B131" s="17" t="s">
+      <c r="B131" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D131" s="27"/>
-      <c r="E131" s="28"/>
+      <c r="D131" s="26"/>
+      <c r="E131" s="27"/>
     </row>
     <row r="132" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A132" s="10">
         <v>108</v>
       </c>
-      <c r="B132" s="17" t="s">
+      <c r="B132" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D132" s="27"/>
-      <c r="E132" s="28"/>
+      <c r="D132" s="26"/>
+      <c r="E132" s="27"/>
     </row>
     <row r="133" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A133" s="10">
         <v>109</v>
       </c>
-      <c r="B133" s="17" t="s">
+      <c r="B133" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D133" s="27"/>
-      <c r="E133" s="28"/>
+      <c r="D133" s="26"/>
+      <c r="E133" s="27"/>
     </row>
     <row r="134" spans="1:5" ht="54" x14ac:dyDescent="0.25">
       <c r="A134" s="10">
         <v>110</v>
       </c>
-      <c r="B134" s="17" t="s">
+      <c r="B134" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D134" s="27"/>
-      <c r="E134" s="28"/>
+      <c r="D134" s="26"/>
+      <c r="E134" s="27"/>
     </row>
     <row r="135" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A135" s="10">
         <v>111</v>
       </c>
-      <c r="B135" s="17" t="s">
+      <c r="B135" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D135" s="27"/>
-      <c r="E135" s="28"/>
+      <c r="D135" s="26"/>
+      <c r="E135" s="27"/>
     </row>
     <row r="136" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A136" s="10">
         <v>112</v>
       </c>
-      <c r="B136" s="17" t="s">
+      <c r="B136" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D136" s="27"/>
-      <c r="E136" s="28"/>
+      <c r="D136" s="26"/>
+      <c r="E136" s="27"/>
     </row>
     <row r="137" spans="1:5" ht="81" x14ac:dyDescent="0.25">
       <c r="A137" s="10">
         <v>113</v>
       </c>
-      <c r="B137" s="18" t="s">
+      <c r="B137" s="17" t="s">
         <v>108</v>
       </c>
       <c r="C137" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="D137" s="27"/>
-      <c r="E137" s="28"/>
+      <c r="D137" s="26"/>
+      <c r="E137" s="27"/>
     </row>
     <row r="138" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A138" s="10">
         <v>114</v>
       </c>
-      <c r="B138" s="17" t="s">
+      <c r="B138" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D138" s="27"/>
-      <c r="E138" s="28"/>
+      <c r="D138" s="26"/>
+      <c r="E138" s="27"/>
     </row>
     <row r="139" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A139" s="10">
         <v>115</v>
       </c>
-      <c r="B139" s="17" t="s">
+      <c r="B139" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C139" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D139" s="27"/>
-      <c r="E139" s="28"/>
+      <c r="D139" s="26"/>
+      <c r="E139" s="27"/>
     </row>
     <row r="140" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A140" s="10">
         <v>116</v>
       </c>
-      <c r="B140" s="17" t="s">
+      <c r="B140" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="D140" s="27"/>
-      <c r="E140" s="28"/>
+      <c r="D140" s="26"/>
+      <c r="E140" s="27"/>
     </row>
     <row r="141" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A141" s="10">
         <v>117</v>
       </c>
-      <c r="B141" s="17" t="s">
+      <c r="B141" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C141" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D141" s="27"/>
-      <c r="E141" s="28"/>
+      <c r="D141" s="26"/>
+      <c r="E141" s="27"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="4"/>
+      <c r="B142" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C142" s="9"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="9"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
+        <v>118</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D143" s="26"/>
+      <c r="E143" s="27"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="16" t="s">
-        <v>204</v>
-      </c>
+      <c r="A144" s="6">
+        <v>119</v>
+      </c>
+      <c r="B144" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D144" s="26"/>
+      <c r="E144" s="27"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B145" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D145" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="E145" s="23" t="s">
-        <v>215</v>
-      </c>
+      <c r="A145" s="6">
+        <v>120</v>
+      </c>
+      <c r="B145" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D145" s="26"/>
+      <c r="E145" s="27"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="4"/>
       <c r="B146" s="5" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C146" s="9"/>
       <c r="D146" s="4"/>
@@ -3029,1387 +2859,308 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D147" s="27"/>
-      <c r="E147" s="28"/>
-    </row>
-    <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="D147" s="26"/>
+      <c r="E147" s="27"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
-        <v>2</v>
-      </c>
-      <c r="B148" s="17" t="s">
-        <v>126</v>
+        <v>122</v>
+      </c>
+      <c r="B148" s="16" t="s">
+        <v>133</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D148" s="27"/>
-      <c r="E148" s="28"/>
+        <v>135</v>
+      </c>
+      <c r="D148" s="26"/>
+      <c r="E148" s="27"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="6">
-        <v>3</v>
-      </c>
-      <c r="B149" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C149" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D149" s="27"/>
-      <c r="E149" s="28"/>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="4"/>
+      <c r="B149" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C149" s="9"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="9"/>
+    </row>
+    <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
-        <v>4</v>
-      </c>
-      <c r="B150" s="17" t="s">
-        <v>126</v>
+        <v>123</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="D150" s="27"/>
-      <c r="E150" s="28"/>
+        <v>136</v>
+      </c>
+      <c r="D150" s="26"/>
+      <c r="E150" s="27"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
-        <v>5</v>
-      </c>
-      <c r="B151" s="17" t="s">
-        <v>126</v>
+        <v>124</v>
+      </c>
+      <c r="B151" s="16" t="s">
+        <v>157</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D151" s="27"/>
-      <c r="E151" s="28"/>
+        <v>148</v>
+      </c>
+      <c r="D151" s="26"/>
+      <c r="E151" s="27"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
-        <v>6</v>
-      </c>
-      <c r="B152" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
+      </c>
+      <c r="B152" s="16" t="s">
+        <v>157</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D152" s="27"/>
-      <c r="E152" s="28"/>
+        <v>145</v>
+      </c>
+      <c r="D152" s="26"/>
+      <c r="E152" s="27"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
-        <v>7</v>
-      </c>
-      <c r="B153" s="17" t="s">
         <v>126</v>
       </c>
+      <c r="B153" s="16" t="s">
+        <v>157</v>
+      </c>
       <c r="C153" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D153" s="27"/>
-      <c r="E153" s="28"/>
+        <v>146</v>
+      </c>
+      <c r="D153" s="26"/>
+      <c r="E153" s="27"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
-        <v>8</v>
-      </c>
-      <c r="B154" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B154" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D154" s="26"/>
+      <c r="E154" s="27"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="4"/>
+      <c r="B155" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C155" s="9"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="9"/>
+    </row>
+    <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+      <c r="A156" s="6">
+        <v>128</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D156" s="26"/>
+      <c r="E156" s="29"/>
+    </row>
+    <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+      <c r="A157" s="4"/>
+      <c r="B157" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C157" s="9"/>
+      <c r="D157" s="4"/>
+      <c r="E157" s="9"/>
+    </row>
+    <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+      <c r="A158" s="6">
+        <v>129</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D158" s="26"/>
+      <c r="E158" s="27"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="4"/>
+      <c r="B159" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C154" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D154" s="27"/>
-      <c r="E154" s="28"/>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="6">
-        <v>9</v>
-      </c>
-      <c r="B155" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C155" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="D155" s="27"/>
-      <c r="E155" s="28"/>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="6">
-        <v>10</v>
-      </c>
-      <c r="B156" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C156" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D156" s="27"/>
-      <c r="E156" s="28"/>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="6">
-        <v>11</v>
-      </c>
-      <c r="B157" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C157" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D157" s="27"/>
-      <c r="E157" s="28"/>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="6">
-        <v>12</v>
-      </c>
-      <c r="B158" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C158" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D158" s="27"/>
-      <c r="E158" s="28"/>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="6">
-        <v>13</v>
-      </c>
-      <c r="B159" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C159" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D159" s="27"/>
-      <c r="E159" s="28"/>
+      <c r="C159" s="9"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="9"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
-        <v>14</v>
-      </c>
-      <c r="B160" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B160" s="7" t="s">
         <v>126</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D160" s="27"/>
-      <c r="E160" s="28"/>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="6">
-        <v>15</v>
-      </c>
-      <c r="B161" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C161" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D161" s="27"/>
-      <c r="E161" s="28"/>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="6">
-        <v>16</v>
-      </c>
-      <c r="B162" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C162" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D162" s="27"/>
-      <c r="E162" s="28"/>
+        <v>159</v>
+      </c>
+      <c r="D160" s="26"/>
+      <c r="E160" s="27"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="6">
-        <v>17</v>
-      </c>
-      <c r="B163" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C163" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D163" s="27"/>
-      <c r="E163" s="28"/>
+      <c r="A163" s="19" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="6">
-        <v>18</v>
-      </c>
-      <c r="B164" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C164" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D164" s="27"/>
-      <c r="E164" s="28"/>
+      <c r="A164" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D164" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="E164" s="22" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="6">
-        <v>19</v>
-      </c>
-      <c r="B165" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C165" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D165" s="27"/>
-      <c r="E165" s="28"/>
+      <c r="A165" s="32">
+        <v>1</v>
+      </c>
+      <c r="B165" s="29"/>
+      <c r="C165" s="29"/>
+      <c r="D165" s="28"/>
+      <c r="E165" s="29"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
-        <v>20</v>
-      </c>
-      <c r="B166" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C166" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D166" s="27"/>
-      <c r="E166" s="28"/>
+        <v>2</v>
+      </c>
+      <c r="B166" s="29"/>
+      <c r="C166" s="29"/>
+      <c r="D166" s="28"/>
+      <c r="E166" s="29"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="4"/>
-      <c r="B167" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C167" s="9"/>
-      <c r="D167" s="4"/>
-      <c r="E167" s="9"/>
+      <c r="A167" s="6">
+        <v>3</v>
+      </c>
+      <c r="B167" s="29"/>
+      <c r="C167" s="29"/>
+      <c r="D167" s="28"/>
+      <c r="E167" s="29"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
-        <v>21</v>
-      </c>
-      <c r="B168" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C168" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="D168" s="27"/>
-      <c r="E168" s="28"/>
-    </row>
-    <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A169" s="6">
-        <v>22</v>
-      </c>
-      <c r="B169" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C169" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D169" s="27"/>
-      <c r="E169" s="28"/>
+        <v>4</v>
+      </c>
+      <c r="B168" s="29"/>
+      <c r="C168" s="29"/>
+      <c r="D168" s="28"/>
+      <c r="E168" s="29"/>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="32">
+        <v>5</v>
+      </c>
+      <c r="B169" s="29"/>
+      <c r="C169" s="29"/>
+      <c r="D169" s="28"/>
+      <c r="E169" s="29"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="6">
-        <v>23</v>
-      </c>
-      <c r="B170" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C170" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D170" s="27"/>
-      <c r="E170" s="28"/>
+      <c r="A170" s="32">
+        <v>6</v>
+      </c>
+      <c r="B170" s="29"/>
+      <c r="C170" s="29"/>
+      <c r="D170" s="28"/>
+      <c r="E170" s="29"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
-        <v>24</v>
-      </c>
-      <c r="B171" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C171" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D171" s="27"/>
-      <c r="E171" s="28"/>
+        <v>7</v>
+      </c>
+      <c r="B171" s="29"/>
+      <c r="C171" s="29"/>
+      <c r="D171" s="28"/>
+      <c r="E171" s="29"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
-        <v>25</v>
-      </c>
-      <c r="B172" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C172" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D172" s="27"/>
-      <c r="E172" s="28"/>
+        <v>8</v>
+      </c>
+      <c r="B172" s="29"/>
+      <c r="C172" s="29"/>
+      <c r="D172" s="28"/>
+      <c r="E172" s="29"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
-        <v>26</v>
-      </c>
-      <c r="B173" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C173" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B173" s="29"/>
+      <c r="C173" s="29"/>
+      <c r="D173" s="28"/>
+      <c r="E173" s="29"/>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="6">
+        <v>10</v>
+      </c>
+      <c r="B174" s="29"/>
+      <c r="C174" s="29"/>
+      <c r="D174" s="28"/>
+      <c r="E174" s="29"/>
+    </row>
+    <row r="178" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B178" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="D173" s="27"/>
-      <c r="E173" s="28"/>
-    </row>
-    <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A174" s="4"/>
-      <c r="B174" s="5" t="s">
+      <c r="E178" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="C174" s="9"/>
-      <c r="D174" s="4"/>
-      <c r="E174" s="9"/>
-    </row>
-    <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A175" s="6">
-        <v>27</v>
-      </c>
-      <c r="B175" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C175" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="D175" s="27"/>
-      <c r="E175" s="28"/>
-    </row>
-    <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A176" s="6">
-        <v>28</v>
-      </c>
-      <c r="B176" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C176" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D176" s="27"/>
-      <c r="E176" s="28"/>
-    </row>
-    <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A177" s="6">
-        <v>29</v>
-      </c>
-      <c r="B177" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C177" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="D177" s="27"/>
-      <c r="E177" s="28"/>
-    </row>
-    <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A178" s="6">
-        <v>30</v>
-      </c>
-      <c r="B178" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="C178" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D178" s="27"/>
-      <c r="E178" s="28"/>
-    </row>
-    <row r="179" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A179" s="6">
-        <v>31</v>
-      </c>
-      <c r="B179" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C179" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D179" s="27"/>
-      <c r="E179" s="28"/>
-    </row>
-    <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A180" s="6">
-        <v>32</v>
-      </c>
-      <c r="B180" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C180" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D180" s="27"/>
-      <c r="E180" s="28"/>
-    </row>
-    <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A181" s="6">
-        <v>33</v>
-      </c>
-      <c r="B181" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C181" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D181" s="27"/>
-      <c r="E181" s="28"/>
-    </row>
-    <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A182" s="6">
-        <v>34</v>
-      </c>
-      <c r="B182" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C182" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D182" s="27"/>
-      <c r="E182" s="28"/>
-    </row>
-    <row r="183" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A183" s="6">
-        <v>35</v>
-      </c>
-      <c r="B183" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C183" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="D183" s="27"/>
-      <c r="E183" s="28"/>
-    </row>
-    <row r="184" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A184" s="6">
-        <v>36</v>
-      </c>
-      <c r="B184" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C184" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D184" s="27"/>
-      <c r="E184" s="28"/>
-    </row>
-    <row r="185" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A185" s="6">
-        <v>37</v>
-      </c>
-      <c r="B185" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C185" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D185" s="27"/>
-      <c r="E185" s="28"/>
-    </row>
-    <row r="186" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A186" s="6">
-        <v>38</v>
-      </c>
-      <c r="B186" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C186" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D186" s="27"/>
-      <c r="E186" s="28"/>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" s="4"/>
-      <c r="B187" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C187" s="9"/>
-      <c r="D187" s="4"/>
-      <c r="E187" s="9"/>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" s="6">
-        <v>39</v>
-      </c>
-      <c r="B188" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C188" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D188" s="27"/>
-      <c r="E188" s="28"/>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" s="6">
-        <v>40</v>
-      </c>
-      <c r="B189" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C189" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D189" s="27"/>
-      <c r="E189" s="28"/>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" s="6">
-        <v>41</v>
-      </c>
-      <c r="B190" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C190" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D190" s="27"/>
-      <c r="E190" s="28"/>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" s="6">
-        <v>42</v>
-      </c>
-      <c r="B191" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C191" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D191" s="27"/>
-      <c r="E191" s="28"/>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A192" s="6">
-        <v>43</v>
-      </c>
-      <c r="B192" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C192" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="D192" s="27"/>
-      <c r="E192" s="28"/>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A193" s="6">
-        <v>44</v>
-      </c>
-      <c r="B193" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C193" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D193" s="27"/>
-      <c r="E193" s="28"/>
-    </row>
-    <row r="194" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A194" s="6">
-        <v>45</v>
-      </c>
-      <c r="B194" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C194" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="D194" s="27"/>
-      <c r="E194" s="28"/>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A195" s="6">
-        <v>46</v>
-      </c>
-      <c r="B195" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C195" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D195" s="27"/>
-      <c r="E195" s="28"/>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A196" s="6">
-        <v>47</v>
-      </c>
-      <c r="B196" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C196" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D196" s="27"/>
-      <c r="E196" s="28"/>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A197" s="6">
-        <v>48</v>
-      </c>
-      <c r="B197" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C197" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D197" s="27"/>
-      <c r="E197" s="28"/>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A198" s="6">
-        <v>49</v>
-      </c>
-      <c r="B198" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C198" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D198" s="27"/>
-      <c r="E198" s="28"/>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A199" s="6">
-        <v>50</v>
-      </c>
-      <c r="B199" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C199" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D199" s="27"/>
-      <c r="E199" s="28"/>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A200" s="6">
-        <v>51</v>
-      </c>
-      <c r="B200" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C200" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D200" s="27"/>
-      <c r="E200" s="28"/>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A201" s="6">
-        <v>52</v>
-      </c>
-      <c r="B201" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C201" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D201" s="27"/>
-      <c r="E201" s="28"/>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A202" s="6">
-        <v>53</v>
-      </c>
-      <c r="B202" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C202" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D202" s="27"/>
-      <c r="E202" s="28"/>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A203" s="4"/>
-      <c r="B203" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C203" s="9"/>
-      <c r="D203" s="4"/>
-      <c r="E203" s="9"/>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A204" s="6">
-        <v>54</v>
-      </c>
-      <c r="B204" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C204" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D204" s="27"/>
-      <c r="E204" s="28"/>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A205" s="6">
-        <v>55</v>
-      </c>
-      <c r="B205" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="C205" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D205" s="27"/>
-      <c r="E205" s="28"/>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A206" s="6">
-        <v>56</v>
-      </c>
-      <c r="B206" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="C206" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D206" s="27"/>
-      <c r="E206" s="28"/>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A207" s="6">
-        <v>57</v>
-      </c>
-      <c r="B207" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="C207" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D207" s="27"/>
-      <c r="E207" s="28"/>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A208" s="6">
-        <v>58</v>
-      </c>
-      <c r="B208" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="C208" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="D208" s="27"/>
-      <c r="E208" s="28"/>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" s="6">
-        <v>59</v>
-      </c>
-      <c r="B209" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="C209" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D209" s="27"/>
-      <c r="E209" s="28"/>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A210" s="6">
-        <v>60</v>
-      </c>
-      <c r="B210" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="C210" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D210" s="27"/>
-      <c r="E210" s="28"/>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A211" s="6">
-        <v>61</v>
-      </c>
-      <c r="B211" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="C211" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="D211" s="27"/>
-      <c r="E211" s="28"/>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A212" s="6">
-        <v>62</v>
-      </c>
-      <c r="B212" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="C212" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D212" s="27"/>
-      <c r="E212" s="28"/>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A213" s="4"/>
-      <c r="B213" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C213" s="9"/>
-      <c r="D213" s="4"/>
-      <c r="E213" s="9"/>
-    </row>
-    <row r="214" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A214" s="6">
-        <v>63</v>
-      </c>
-      <c r="B214" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C214" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D214" s="27"/>
-      <c r="E214" s="28"/>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A215" s="6">
-        <v>64</v>
-      </c>
-      <c r="B215" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="C215" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D215" s="27"/>
-      <c r="E215" s="28"/>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A216" s="4"/>
-      <c r="B216" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C216" s="9"/>
-      <c r="D216" s="4"/>
-      <c r="E216" s="9"/>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" s="6">
-        <v>65</v>
-      </c>
-      <c r="B217" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C217" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D217" s="27"/>
-      <c r="E217" s="28"/>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" s="6">
-        <v>66</v>
-      </c>
-      <c r="B218" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="C218" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D218" s="27"/>
-      <c r="E218" s="28"/>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" s="4"/>
-      <c r="B219" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C219" s="9"/>
-      <c r="D219" s="4"/>
-      <c r="E219" s="9"/>
-    </row>
-    <row r="220" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A220" s="6">
-        <v>67</v>
-      </c>
-      <c r="B220" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C220" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D220" s="27"/>
-      <c r="E220" s="28"/>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A221" s="6">
-        <v>68</v>
-      </c>
-      <c r="B221" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="C221" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="D221" s="27"/>
-      <c r="E221" s="28"/>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A222" s="6">
-        <v>69</v>
-      </c>
-      <c r="B222" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="C222" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="D222" s="27"/>
-      <c r="E222" s="28"/>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A223" s="6">
-        <v>70</v>
-      </c>
-      <c r="B223" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="C223" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="D223" s="27"/>
-      <c r="E223" s="28"/>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A224" s="6">
-        <v>71</v>
-      </c>
-      <c r="B224" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="C224" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="D224" s="27"/>
-      <c r="E224" s="28"/>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A225" s="6">
-        <v>72</v>
-      </c>
-      <c r="B225" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="C225" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="D225" s="27"/>
-      <c r="E225" s="28"/>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A226" s="6">
-        <v>73</v>
-      </c>
-      <c r="B226" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="C226" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="D226" s="27"/>
-      <c r="E226" s="28"/>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A227" s="6">
-        <v>74</v>
-      </c>
-      <c r="B227" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="C227" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="D227" s="27"/>
-      <c r="E227" s="28"/>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A230" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A231" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B231" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="C231" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D231" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="E231" s="23" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A232" s="34">
-        <v>1</v>
-      </c>
-      <c r="B232" s="31"/>
-      <c r="C232" s="31"/>
-      <c r="D232" s="30"/>
-      <c r="E232" s="31"/>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A233" s="6">
-        <v>2</v>
-      </c>
-      <c r="B233" s="29"/>
-      <c r="C233" s="28"/>
-      <c r="D233" s="27"/>
-      <c r="E233" s="28"/>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A234" s="6">
-        <v>3</v>
-      </c>
-      <c r="B234" s="28"/>
-      <c r="C234" s="28"/>
-      <c r="D234" s="27"/>
-      <c r="E234" s="28"/>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A235" s="6">
-        <v>4</v>
-      </c>
-      <c r="B235" s="29"/>
-      <c r="C235" s="28"/>
-      <c r="D235" s="27"/>
-      <c r="E235" s="28"/>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A236" s="34">
-        <v>5</v>
-      </c>
-      <c r="B236" s="31"/>
-      <c r="C236" s="31"/>
-      <c r="D236" s="30"/>
-      <c r="E236" s="31"/>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A237" s="34">
-        <v>6</v>
-      </c>
-      <c r="B237" s="31"/>
-      <c r="C237" s="31"/>
-      <c r="D237" s="30"/>
-      <c r="E237" s="31"/>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A238" s="6">
-        <v>7</v>
-      </c>
-      <c r="B238" s="29"/>
-      <c r="C238" s="28"/>
-      <c r="D238" s="27"/>
-      <c r="E238" s="28"/>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A239" s="6">
-        <v>8</v>
-      </c>
-      <c r="B239" s="28"/>
-      <c r="C239" s="28"/>
-      <c r="D239" s="27"/>
-      <c r="E239" s="28"/>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A240" s="6">
-        <v>9</v>
-      </c>
-      <c r="B240" s="28"/>
-      <c r="C240" s="28"/>
-      <c r="D240" s="27"/>
-      <c r="E240" s="28"/>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A241" s="6">
-        <v>10</v>
-      </c>
-      <c r="B241" s="28"/>
-      <c r="C241" s="28"/>
-      <c r="D241" s="27"/>
-      <c r="E241" s="28"/>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A242" s="6">
-        <v>11</v>
-      </c>
-      <c r="B242" s="28"/>
-      <c r="C242" s="28"/>
-      <c r="D242" s="27"/>
-      <c r="E242" s="28"/>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A243" s="6">
-        <v>12</v>
-      </c>
-      <c r="B243" s="28"/>
-      <c r="C243" s="28"/>
-      <c r="D243" s="27"/>
-      <c r="E243" s="28"/>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A244" s="6">
-        <v>13</v>
-      </c>
-      <c r="B244" s="28"/>
-      <c r="C244" s="28"/>
-      <c r="D244" s="27"/>
-      <c r="E244" s="28"/>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A245" s="6">
-        <v>14</v>
-      </c>
-      <c r="B245" s="28"/>
-      <c r="C245" s="28"/>
-      <c r="D245" s="27"/>
-      <c r="E245" s="28"/>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A246" s="6">
-        <v>15</v>
-      </c>
-      <c r="B246" s="28"/>
-      <c r="C246" s="28"/>
-      <c r="D246" s="27"/>
-      <c r="E246" s="28"/>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A247" s="6">
-        <v>16</v>
-      </c>
-      <c r="B247" s="28"/>
-      <c r="C247" s="28"/>
-      <c r="D247" s="27"/>
-      <c r="E247" s="28"/>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A248" s="6">
-        <v>17</v>
-      </c>
-      <c r="B248" s="28"/>
-      <c r="C248" s="28"/>
-      <c r="D248" s="27"/>
-      <c r="E248" s="28"/>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A249" s="6">
-        <v>18</v>
-      </c>
-      <c r="B249" s="28"/>
-      <c r="C249" s="28"/>
-      <c r="D249" s="27"/>
-      <c r="E249" s="28"/>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A250" s="6">
-        <v>19</v>
-      </c>
-      <c r="B250" s="28"/>
-      <c r="C250" s="28"/>
-      <c r="D250" s="27"/>
-      <c r="E250" s="28"/>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A251" s="6">
-        <v>20</v>
-      </c>
-      <c r="B251" s="28"/>
-      <c r="C251" s="28"/>
-      <c r="D251" s="27"/>
-      <c r="E251" s="28"/>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A252" s="6">
-        <v>21</v>
-      </c>
-      <c r="B252" s="28"/>
-      <c r="C252" s="28"/>
-      <c r="D252" s="27"/>
-      <c r="E252" s="28"/>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A253" s="6">
-        <v>22</v>
-      </c>
-      <c r="B253" s="28"/>
-      <c r="C253" s="28"/>
-      <c r="D253" s="27"/>
-      <c r="E253" s="28"/>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A254" s="6">
-        <v>23</v>
-      </c>
-      <c r="B254" s="28"/>
-      <c r="C254" s="28"/>
-      <c r="D254" s="27"/>
-      <c r="E254" s="28"/>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A255" s="6">
-        <v>24</v>
-      </c>
-      <c r="B255" s="28"/>
-      <c r="C255" s="28"/>
-      <c r="D255" s="27"/>
-      <c r="E255" s="28"/>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A256" s="6">
-        <v>25</v>
-      </c>
-      <c r="B256" s="28"/>
-      <c r="C256" s="28"/>
-      <c r="D256" s="27"/>
-      <c r="E256" s="28"/>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A257" s="6">
-        <v>26</v>
-      </c>
-      <c r="B257" s="28"/>
-      <c r="C257" s="28"/>
-      <c r="D257" s="27"/>
-      <c r="E257" s="28"/>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A258" s="6">
-        <v>27</v>
-      </c>
-      <c r="B258" s="28"/>
-      <c r="C258" s="28"/>
-      <c r="D258" s="27"/>
-      <c r="E258" s="28"/>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A259" s="6">
-        <v>28</v>
-      </c>
-      <c r="B259" s="28"/>
-      <c r="C259" s="28"/>
-      <c r="D259" s="27"/>
-      <c r="E259" s="28"/>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A260" s="6">
-        <v>29</v>
-      </c>
-      <c r="B260" s="28"/>
-      <c r="C260" s="28"/>
-      <c r="D260" s="27"/>
-      <c r="E260" s="28"/>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A261" s="6">
-        <v>30</v>
-      </c>
-      <c r="B261" s="28"/>
-      <c r="C261" s="28"/>
-      <c r="D261" s="27"/>
-      <c r="E261" s="28"/>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A262" s="6">
-        <v>31</v>
-      </c>
-      <c r="B262" s="28"/>
-      <c r="C262" s="28"/>
-      <c r="D262" s="27"/>
-      <c r="E262" s="28"/>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A263" s="6">
-        <v>32</v>
-      </c>
-      <c r="B263" s="28"/>
-      <c r="C263" s="28"/>
-      <c r="D263" s="27"/>
-      <c r="E263" s="28"/>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A264" s="6">
-        <v>33</v>
-      </c>
-      <c r="B264" s="28"/>
-      <c r="C264" s="28"/>
-      <c r="D264" s="27"/>
-      <c r="E264" s="28"/>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A265" s="6">
-        <v>34</v>
-      </c>
-      <c r="B265" s="31"/>
-      <c r="C265" s="28"/>
-      <c r="D265" s="27"/>
-      <c r="E265" s="28"/>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A266" s="34">
-        <v>35</v>
-      </c>
-      <c r="B266" s="31"/>
-      <c r="C266" s="31"/>
-      <c r="D266" s="30"/>
-      <c r="E266" s="31"/>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B272" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="E272" s="21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="273" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B273" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="E273" s="22" t="s">
-        <v>202</v>
+    </row>
+    <row r="179" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B179" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="E179" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="HvRAf25CLSZbbFeu4NyonlOOTrWUVWbsflLx2UPDyIuNhU26JPa6HHvUjdApuTQbp6FxR+5eeStUWMt/I8PgWQ==" saltValue="paFxnAahN2vB2U0PA8cOvw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vpRrRUpg1Hqy8J/5TTtTveH87Jd1zhTLpIWGtU70UxXJVTZfuWni+amMpmza70rqDTbGdLDxiL5swTZtsNuMAg==" saltValue="ks/q9X81NXqp3ymo34O35Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A10:E10"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14:D23 D25:D26 D28:D73 D75:D78 D80:D94 D96:D99 D101:D104 D106:D109 D111:D114 D116:D118 D120:D123 D125:D141 D143:D145 D147:D148 D150:D154 D156 D158 D160 D165:D174" xr:uid="{FD20753E-F145-4E82-97CE-E32E6A1C63CD}">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
